--- a/data/trans_bre/IP07_C13_R_2023-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP07_C13_R_2023-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,297 +619,295 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,46</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>53,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-7,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.132898989612931</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>5.463836307255489</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.6809573387699954</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.1774090935399576</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.533648672675757</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.4393675241321634</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.07500151380321111</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.04574108919891772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,35; 6,42</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,24; 12,72</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,38; 3,75</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-5,14; 5,79</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-42,64; 305,61</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-9,78; 143,72</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-53,79; 57,92</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-82,53; 480,94</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.353289583858128</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.235479671440495</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.377805165773038</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-5.13996711356978</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4264074784385056</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.09775206565217991</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.5378998758326018</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.8253208501627042</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.415861318042208</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.72156651927507</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.751695163274339</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.788622950951654</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>3.056135339073374</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.437155517193277</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.579203863943793</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>4.809370981829578</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>12-15</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,15</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,51</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>16,82%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-10,41%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>499,83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,52; 4,18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,78; 7,06</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-7,23; 4,38</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,91; 7,29</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-50,41; 170,15</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-29,44; 87,98</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-52,8; 54,68</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-49,49; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.7033027716831924</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.708164268476885</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.152299787469535</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3.512420253604957</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1682212356712802</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1550143071694479</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1041394931391434</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>4.99828028540384</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>30,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-9,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>122,78%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.515102483552775</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.778299204942799</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-7.234289614090117</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.9062284078298524</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5040926560767596</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2944213341053918</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5279794865884827</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4949341342489464</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,23; 4,05</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,82; 7,88</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,68; 2,94</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,12; 5,92</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-25,9; 139,95</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-7,65; 77,65</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-38,98; 36,91</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-21,64; 663,43</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.184047186740624</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.061160135358284</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.379946923755136</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7.294974461016773</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.701542975011531</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.8797990012041349</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.5467619650164388</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1.256523321234811</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.519862792742411</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.9290477197198401</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.291262253806713</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.3059147818965136</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.3010424907979359</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.09244894810078427</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1.227772544485084</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.232059047718384</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.821895554488716</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.680261354169793</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.121394541852949</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2589787479455485</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.07650656857161593</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.389843931856632</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2163652148189736</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.054320322328077</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.876324349366472</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.939975814443715</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.919708239842252</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.399483390345514</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.7765316556841709</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.3690811556803936</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>6.634316962236261</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -908,11 +915,11 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
